--- a/facultad-derecho/plantillas/Martes.xlsx
+++ b/facultad-derecho/plantillas/Martes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\Proyecto\APLICATIVOS-FACULTAD-DE-DERECHO\facultad-derecho\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FAAD38-3164-4D8E-BFB1-4EF4AC145AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86691809-6882-4987-8DB7-115C7659EFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASIGNACIÓN TURNOS" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="260">
   <si>
     <t>UNIVERSIDAD COLEGIO MAYOR DE CUNDINAMARCA</t>
   </si>
@@ -801,40 +801,16 @@
     <t>VELANDIA CANOSA EDUARDO ANDRES</t>
   </si>
   <si>
-    <t xml:space="preserve">ANDRES RICARDO MORENO SANGUINO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NELSON ENRIQUE RUEDA RODRIGUEZ </t>
-  </si>
-  <si>
     <t>LISTADO DE ASIGNACION DE TURNOS PARA ESTUDIANTES  PERIODO  2025-II</t>
   </si>
   <si>
     <t>MIERCOLES</t>
   </si>
   <si>
-    <t>LINA PAOLA TRIANA MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROBERTO ANGEL BADRAN BLANCO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALVARO FAJARDO PINILLA</t>
-  </si>
-  <si>
-    <t>ROSEMBER SIERRA AVILA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROCIO DEL PILAR ROJAS ROCHA </t>
-  </si>
-  <si>
     <t>CJ</t>
   </si>
   <si>
     <t>SEMANA No. 7 SEPTIEMBRE 08-12</t>
-  </si>
-  <si>
-    <t>WILLIAM GIOVANNI MORENO AVILA</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1058,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1497,6 +1473,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1508,7 +1565,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1864,27 +1921,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1896,9 +1935,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="13" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1920,8 +1956,34 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="5" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="5" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1949,6 +2011,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1958,12 +2026,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1979,12 +2041,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2002,6 +2058,39 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2424,81 +2513,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K480"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" customWidth="1"/>
+    <col min="2" max="2" width="42.7265625" customWidth="1"/>
     <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" customWidth="1"/>
+    <col min="6" max="6" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="174" t="s">
+    <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="176"/>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="177" t="s">
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="177"/>
+    </row>
+    <row r="2" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="179"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="177" t="s">
+      <c r="B2" s="179"/>
+      <c r="C2" s="179"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="180"/>
+    </row>
+    <row r="3" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="178"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="179"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="177" t="s">
+      <c r="B3" s="179"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="180"/>
+    </row>
+    <row r="4" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="178" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="178"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="179"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="177" t="s">
+      <c r="B4" s="179"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="180"/>
+    </row>
+    <row r="5" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="178" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="178"/>
-      <c r="G5" s="179"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="171"/>
-      <c r="B6" s="172"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="173"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="179"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="180"/>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="172"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="173"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="174"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
         <v>3</v>
       </c>
@@ -2521,7 +2610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="21">
         <v>1</v>
       </c>
@@ -2542,7 +2631,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="21">
         <v>2</v>
       </c>
@@ -2563,7 +2652,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="21">
         <v>3</v>
       </c>
@@ -2584,7 +2673,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="21">
         <v>4</v>
       </c>
@@ -2605,7 +2694,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="21">
         <v>5</v>
       </c>
@@ -2626,7 +2715,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="21">
         <v>6</v>
       </c>
@@ -2647,7 +2736,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="21">
         <v>7</v>
       </c>
@@ -2668,7 +2757,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="21">
         <v>8</v>
       </c>
@@ -2689,7 +2778,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="62"/>
       <c r="B16" s="58"/>
       <c r="C16" s="59"/>
@@ -2703,7 +2792,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="21">
         <v>9</v>
       </c>
@@ -2724,7 +2813,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="21">
         <v>10</v>
       </c>
@@ -2745,7 +2834,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="21">
         <v>11</v>
       </c>
@@ -2766,7 +2855,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="21">
         <v>12</v>
       </c>
@@ -2787,7 +2876,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="21">
         <v>13</v>
       </c>
@@ -2808,7 +2897,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="21">
         <v>14</v>
       </c>
@@ -2829,7 +2918,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="21">
         <v>15</v>
       </c>
@@ -2850,7 +2939,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="54">
         <v>16</v>
       </c>
@@ -2871,7 +2960,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="27">
         <v>17</v>
       </c>
@@ -2892,7 +2981,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="27">
         <v>18</v>
       </c>
@@ -2913,7 +3002,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="27">
         <v>19</v>
       </c>
@@ -2934,7 +3023,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="27">
         <v>20</v>
       </c>
@@ -2955,7 +3044,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="27">
         <v>21</v>
       </c>
@@ -2976,7 +3065,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="27">
         <v>22</v>
       </c>
@@ -2997,7 +3086,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="27">
         <v>23</v>
       </c>
@@ -3018,7 +3107,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="27">
         <v>24</v>
       </c>
@@ -3039,7 +3128,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="57"/>
       <c r="B33" s="58"/>
       <c r="C33" s="59"/>
@@ -3053,7 +3142,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="27">
         <v>25</v>
       </c>
@@ -3074,7 +3163,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="27">
         <v>26</v>
       </c>
@@ -3095,7 +3184,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="27">
         <v>27</v>
       </c>
@@ -3116,7 +3205,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="27">
         <v>28</v>
       </c>
@@ -3137,7 +3226,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="27">
         <v>29</v>
       </c>
@@ -3158,7 +3247,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="27">
         <v>30</v>
       </c>
@@ -3179,7 +3268,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="27">
         <v>31</v>
       </c>
@@ -3200,7 +3289,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="48">
         <v>32</v>
       </c>
@@ -3221,7 +3310,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="27">
         <v>33</v>
       </c>
@@ -3242,7 +3331,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="27">
         <v>34</v>
       </c>
@@ -3263,7 +3352,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="27">
         <v>36</v>
       </c>
@@ -3284,7 +3373,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="27">
         <v>37</v>
       </c>
@@ -3305,7 +3394,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="27">
         <v>39</v>
       </c>
@@ -3326,7 +3415,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="27">
         <v>40</v>
       </c>
@@ -3347,7 +3436,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="27">
         <v>42</v>
       </c>
@@ -3368,7 +3457,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="27">
         <v>43</v>
       </c>
@@ -3389,7 +3478,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="27"/>
       <c r="B50" s="9"/>
       <c r="D50" s="14" t="s">
@@ -3403,7 +3492,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="57"/>
       <c r="B51" s="58"/>
       <c r="C51" s="63"/>
@@ -3417,7 +3506,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="27">
         <v>45</v>
       </c>
@@ -3438,7 +3527,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="27">
         <v>46</v>
       </c>
@@ -3459,7 +3548,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="27"/>
       <c r="B54" s="9"/>
       <c r="C54" s="2"/>
@@ -3474,7 +3563,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="27">
         <v>48</v>
       </c>
@@ -3495,7 +3584,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="27">
         <v>49</v>
       </c>
@@ -3516,7 +3605,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="27">
         <v>51</v>
       </c>
@@ -3537,7 +3626,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="27">
         <v>52</v>
       </c>
@@ -3558,7 +3647,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="27"/>
       <c r="B59" s="9"/>
       <c r="C59" s="2"/>
@@ -3573,7 +3662,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="27">
         <v>54</v>
       </c>
@@ -3594,7 +3683,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="27">
         <v>55</v>
       </c>
@@ -3615,7 +3704,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="27"/>
       <c r="B62" s="9"/>
       <c r="C62" s="2"/>
@@ -3630,7 +3719,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="48">
         <v>56</v>
       </c>
@@ -3645,7 +3734,7 @@
       <c r="F63" s="56"/>
       <c r="G63" s="52"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="27">
         <v>57</v>
       </c>
@@ -3666,7 +3755,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="27">
         <v>58</v>
       </c>
@@ -3687,7 +3776,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="27">
         <v>60</v>
       </c>
@@ -3708,7 +3797,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="27">
         <v>61</v>
       </c>
@@ -3729,7 +3818,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="27">
         <v>63</v>
       </c>
@@ -3751,7 +3840,7 @@
       </c>
       <c r="K68" s="9"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="27">
         <v>64</v>
       </c>
@@ -3772,7 +3861,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="27">
         <v>66</v>
       </c>
@@ -3793,7 +3882,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="27">
         <v>67</v>
       </c>
@@ -3814,7 +3903,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="57"/>
       <c r="B72" s="58"/>
       <c r="C72" s="59"/>
@@ -3828,7 +3917,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="28">
         <v>69</v>
       </c>
@@ -3849,7 +3938,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="10">
         <v>70</v>
       </c>
@@ -3870,7 +3959,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="104"/>
       <c r="B75" s="9"/>
       <c r="C75" s="2"/>
@@ -3881,7 +3970,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="28">
         <v>72</v>
       </c>
@@ -3902,7 +3991,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="10">
         <v>73</v>
       </c>
@@ -3919,7 +4008,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="28">
         <v>75</v>
       </c>
@@ -3940,7 +4029,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="10">
         <v>76</v>
       </c>
@@ -3961,7 +4050,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="104"/>
       <c r="B80" s="9"/>
       <c r="C80" s="2"/>
@@ -3972,7 +4061,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="28">
         <v>78</v>
       </c>
@@ -3993,7 +4082,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="10">
         <v>79</v>
       </c>
@@ -4014,7 +4103,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="104"/>
       <c r="B83" s="9"/>
       <c r="C83" s="2"/>
@@ -4025,7 +4114,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="64">
         <v>80</v>
       </c>
@@ -4040,7 +4129,7 @@
       <c r="F84" s="56"/>
       <c r="G84" s="52"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="27">
         <v>81</v>
       </c>
@@ -4061,7 +4150,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="27">
         <v>82</v>
       </c>
@@ -4082,7 +4171,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="27">
         <v>84</v>
       </c>
@@ -4103,7 +4192,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="27">
         <v>85</v>
       </c>
@@ -4124,7 +4213,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="27">
         <v>87</v>
       </c>
@@ -4145,7 +4234,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="27">
         <v>88</v>
       </c>
@@ -4166,7 +4255,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="27">
         <v>90</v>
       </c>
@@ -4187,7 +4276,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="27">
         <v>91</v>
       </c>
@@ -4208,7 +4297,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="57"/>
       <c r="B93" s="58"/>
       <c r="C93" s="65"/>
@@ -4222,7 +4311,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="27">
         <v>93</v>
       </c>
@@ -4243,7 +4332,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="27">
         <v>94</v>
       </c>
@@ -4264,7 +4353,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="27"/>
       <c r="B96" s="9"/>
       <c r="C96" s="2"/>
@@ -4275,7 +4364,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="27">
         <v>96</v>
       </c>
@@ -4296,7 +4385,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="27">
         <v>97</v>
       </c>
@@ -4317,7 +4406,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="27">
         <v>99</v>
       </c>
@@ -4338,7 +4427,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="27">
         <v>100</v>
       </c>
@@ -4359,7 +4448,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="27"/>
       <c r="B101" s="17"/>
       <c r="C101" s="2"/>
@@ -4372,7 +4461,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="27">
         <v>102</v>
       </c>
@@ -4393,7 +4482,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="27">
         <v>103</v>
       </c>
@@ -4414,7 +4503,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="27"/>
       <c r="B104" s="3"/>
       <c r="C104" s="2"/>
@@ -4427,7 +4516,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="105" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" s="48">
         <v>104</v>
       </c>
@@ -4442,7 +4531,7 @@
       <c r="F105" s="56"/>
       <c r="G105" s="52"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="27">
         <v>105</v>
       </c>
@@ -4463,7 +4552,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="27">
         <v>106</v>
       </c>
@@ -4484,7 +4573,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="27">
         <v>107</v>
       </c>
@@ -4505,7 +4594,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="27">
         <v>108</v>
       </c>
@@ -4526,7 +4615,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="27">
         <v>109</v>
       </c>
@@ -4547,7 +4636,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="27">
         <v>110</v>
       </c>
@@ -4568,7 +4657,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="27">
         <v>111</v>
       </c>
@@ -4589,7 +4678,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="27">
         <v>112</v>
       </c>
@@ -4610,7 +4699,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="27">
         <v>113</v>
       </c>
@@ -4631,7 +4720,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="27">
         <v>114</v>
       </c>
@@ -4652,7 +4741,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="27">
         <v>115</v>
       </c>
@@ -4673,7 +4762,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="27">
         <v>116</v>
       </c>
@@ -4694,7 +4783,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="57"/>
       <c r="B118" s="66"/>
       <c r="C118" s="59"/>
@@ -4708,7 +4797,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="27">
         <v>117</v>
       </c>
@@ -4729,7 +4818,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="27">
         <v>118</v>
       </c>
@@ -4750,7 +4839,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="27">
         <v>119</v>
       </c>
@@ -4771,7 +4860,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="27">
         <v>120</v>
       </c>
@@ -4792,7 +4881,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="27">
         <v>121</v>
       </c>
@@ -4813,7 +4902,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="27">
         <v>122</v>
       </c>
@@ -4834,7 +4923,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="27">
         <v>123</v>
       </c>
@@ -4855,7 +4944,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="27">
         <v>124</v>
       </c>
@@ -4876,7 +4965,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="27">
         <v>125</v>
       </c>
@@ -4897,7 +4986,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="27">
         <v>126</v>
       </c>
@@ -4918,7 +5007,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="27">
         <v>127</v>
       </c>
@@ -4939,7 +5028,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="130" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="48">
         <v>128</v>
       </c>
@@ -4960,7 +5049,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="27">
         <v>129</v>
       </c>
@@ -4981,7 +5070,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="27">
         <v>130</v>
       </c>
@@ -5002,7 +5091,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="27">
         <v>131</v>
       </c>
@@ -5023,7 +5112,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="27">
         <v>132</v>
       </c>
@@ -5044,7 +5133,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="27">
         <v>133</v>
       </c>
@@ -5065,7 +5154,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="27">
         <v>134</v>
       </c>
@@ -5086,7 +5175,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="27">
         <v>135</v>
       </c>
@@ -5107,7 +5196,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="27">
         <v>136</v>
       </c>
@@ -5128,7 +5217,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="27">
         <v>137</v>
       </c>
@@ -5149,7 +5238,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="27">
         <v>138</v>
       </c>
@@ -5170,7 +5259,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="27">
         <v>139</v>
       </c>
@@ -5191,7 +5280,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="27">
         <v>140</v>
       </c>
@@ -5212,7 +5301,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="57"/>
       <c r="B143" s="58"/>
       <c r="C143" s="59"/>
@@ -5226,7 +5315,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="27">
         <v>141</v>
       </c>
@@ -5247,7 +5336,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="27">
         <v>142</v>
       </c>
@@ -5268,7 +5357,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="27">
         <v>143</v>
       </c>
@@ -5289,7 +5378,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="27">
         <v>144</v>
       </c>
@@ -5310,7 +5399,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="27">
         <v>145</v>
       </c>
@@ -5331,7 +5420,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="27">
         <v>146</v>
       </c>
@@ -5352,7 +5441,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="27">
         <v>147</v>
       </c>
@@ -5373,7 +5462,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="27">
         <v>148</v>
       </c>
@@ -5394,7 +5483,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="27">
         <v>149</v>
       </c>
@@ -5415,7 +5504,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="27">
         <v>150</v>
       </c>
@@ -5436,7 +5525,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="27">
         <v>151</v>
       </c>
@@ -5457,7 +5546,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="155" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A155" s="48"/>
       <c r="B155" s="101" t="s">
         <v>236</v>
@@ -5476,7 +5565,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="27"/>
       <c r="B156" s="9"/>
       <c r="C156" s="2"/>
@@ -5489,7 +5578,7 @@
       <c r="F156" s="10"/>
       <c r="G156" s="9"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="27">
         <v>152</v>
       </c>
@@ -5510,7 +5599,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="27">
         <v>153</v>
       </c>
@@ -5531,7 +5620,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="27">
         <v>154</v>
       </c>
@@ -5551,7 +5640,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="27">
         <v>155</v>
       </c>
@@ -5572,7 +5661,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="27">
         <v>156</v>
       </c>
@@ -5593,7 +5682,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="27">
         <v>157</v>
       </c>
@@ -5614,7 +5703,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="57"/>
       <c r="B163" s="58"/>
       <c r="C163" s="59"/>
@@ -5628,7 +5717,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="27">
         <v>158</v>
       </c>
@@ -5649,7 +5738,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="27">
         <v>159</v>
       </c>
@@ -5670,7 +5759,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="27">
         <v>160</v>
       </c>
@@ -5691,7 +5780,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="27">
         <v>161</v>
       </c>
@@ -5712,7 +5801,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="27">
         <v>162</v>
       </c>
@@ -5733,7 +5822,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="27">
         <v>163</v>
       </c>
@@ -5754,7 +5843,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="27">
         <v>164</v>
       </c>
@@ -5775,7 +5864,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="27">
         <v>165</v>
       </c>
@@ -5796,7 +5885,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="27">
         <v>166</v>
       </c>
@@ -5817,7 +5906,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="27">
         <v>167</v>
       </c>
@@ -5838,7 +5927,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="27">
         <v>168</v>
       </c>
@@ -5859,7 +5948,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="175" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A175" s="48">
         <v>169</v>
       </c>
@@ -5879,7 +5968,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="27">
         <v>170</v>
       </c>
@@ -5898,7 +5987,7 @@
       <c r="F176" s="10"/>
       <c r="G176" s="9"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="27">
         <v>171</v>
       </c>
@@ -5917,7 +6006,7 @@
       <c r="F177" s="10"/>
       <c r="G177" s="9"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="27">
         <v>172</v>
       </c>
@@ -5932,7 +6021,7 @@
       <c r="F178" s="10"/>
       <c r="G178" s="9"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="27">
         <v>173</v>
       </c>
@@ -5947,7 +6036,7 @@
       <c r="F179" s="10"/>
       <c r="G179" s="9"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="27">
         <v>174</v>
       </c>
@@ -5962,7 +6051,7 @@
       <c r="F180" s="10"/>
       <c r="G180" s="9"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="27">
         <v>175</v>
       </c>
@@ -5977,7 +6066,7 @@
       <c r="F181" s="10"/>
       <c r="G181" s="9"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="27">
         <v>176</v>
       </c>
@@ -5992,7 +6081,7 @@
       <c r="F182" s="10"/>
       <c r="G182" s="9"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="27">
         <v>177</v>
       </c>
@@ -6007,7 +6096,7 @@
       <c r="F183" s="10"/>
       <c r="G183" s="9"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="27">
         <v>178</v>
       </c>
@@ -6022,7 +6111,7 @@
       <c r="F184" s="10"/>
       <c r="G184" s="9"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="27">
         <v>179</v>
       </c>
@@ -6037,7 +6126,7 @@
       <c r="F185" s="10"/>
       <c r="G185" s="9"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="27">
         <v>180</v>
       </c>
@@ -6052,7 +6141,7 @@
       <c r="F186" s="10"/>
       <c r="G186" s="9"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="27">
         <v>181</v>
       </c>
@@ -6067,7 +6156,7 @@
       <c r="F187" s="10"/>
       <c r="G187" s="9"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="57"/>
       <c r="B188" s="67"/>
       <c r="C188" s="59"/>
@@ -6078,7 +6167,7 @@
       <c r="F188" s="61"/>
       <c r="G188" s="58"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="27">
         <v>182</v>
       </c>
@@ -6093,7 +6182,7 @@
       <c r="F189" s="10"/>
       <c r="G189" s="9"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="27">
         <v>183</v>
       </c>
@@ -6108,7 +6197,7 @@
       <c r="F190" s="10"/>
       <c r="G190" s="15"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="27">
         <v>184</v>
       </c>
@@ -6123,7 +6212,7 @@
       <c r="F191" s="10"/>
       <c r="G191" s="9"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="27">
         <v>185</v>
       </c>
@@ -6138,7 +6227,7 @@
       <c r="F192" s="10"/>
       <c r="G192" s="9"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="27">
         <v>186</v>
       </c>
@@ -6153,7 +6242,7 @@
       <c r="F193" s="10"/>
       <c r="G193" s="9"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="27">
         <v>187</v>
       </c>
@@ -6168,7 +6257,7 @@
       <c r="F194" s="10"/>
       <c r="G194" s="9"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="27">
         <v>188</v>
       </c>
@@ -6183,7 +6272,7 @@
       <c r="F195" s="10"/>
       <c r="G195" s="9"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="27">
         <v>189</v>
       </c>
@@ -6198,7 +6287,7 @@
       <c r="F196" s="10"/>
       <c r="G196" s="9"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="27">
         <v>190</v>
       </c>
@@ -6213,7 +6302,7 @@
       <c r="F197" s="10"/>
       <c r="G197" s="9"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="27">
         <v>191</v>
       </c>
@@ -6228,7 +6317,7 @@
       <c r="F198" s="10"/>
       <c r="G198" s="9"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="27">
         <v>192</v>
       </c>
@@ -6243,7 +6332,7 @@
       <c r="F199" s="10"/>
       <c r="G199" s="9"/>
     </row>
-    <row r="200" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="48">
         <v>193</v>
       </c>
@@ -6258,7 +6347,7 @@
       <c r="F200" s="56"/>
       <c r="G200" s="52"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="27">
         <v>221</v>
       </c>
@@ -6273,7 +6362,7 @@
       <c r="F201" s="10"/>
       <c r="G201" s="9"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="27">
         <v>222</v>
       </c>
@@ -6288,7 +6377,7 @@
       <c r="F202" s="10"/>
       <c r="G202" s="9"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="27">
         <v>223</v>
       </c>
@@ -6303,7 +6392,7 @@
       <c r="F203" s="10"/>
       <c r="G203" s="9"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="27">
         <v>224</v>
       </c>
@@ -6318,7 +6407,7 @@
       <c r="F204" s="10"/>
       <c r="G204" s="9"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="27">
         <v>225</v>
       </c>
@@ -6333,7 +6422,7 @@
       <c r="F205" s="10"/>
       <c r="G205" s="9"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="27">
         <v>226</v>
       </c>
@@ -6348,7 +6437,7 @@
       <c r="F206" s="10"/>
       <c r="G206" s="9"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="27">
         <v>227</v>
       </c>
@@ -6363,7 +6452,7 @@
       <c r="F207" s="10"/>
       <c r="G207" s="9"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="27">
         <v>228</v>
       </c>
@@ -6377,7 +6466,7 @@
       <c r="F208" s="10"/>
       <c r="G208" s="9"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="27">
         <v>229</v>
       </c>
@@ -6392,7 +6481,7 @@
       <c r="F209" s="10"/>
       <c r="G209" s="9"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="27">
         <v>230</v>
       </c>
@@ -6407,7 +6496,7 @@
       <c r="F210" s="10"/>
       <c r="G210" s="9"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="27">
         <v>231</v>
       </c>
@@ -6422,7 +6511,7 @@
       <c r="F211" s="10"/>
       <c r="G211" s="9"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="27">
         <v>232</v>
       </c>
@@ -6437,7 +6526,7 @@
       <c r="F212" s="10"/>
       <c r="G212" s="9"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="27">
         <v>233</v>
       </c>
@@ -6452,7 +6541,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="27">
         <v>234</v>
       </c>
@@ -6467,7 +6556,7 @@
       <c r="F214" s="10"/>
       <c r="G214" s="9"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="27">
         <v>235</v>
       </c>
@@ -6482,7 +6571,7 @@
       <c r="F215" s="10"/>
       <c r="G215" s="9"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="27">
         <v>236</v>
       </c>
@@ -6497,7 +6586,7 @@
       <c r="F216" s="9"/>
       <c r="G216" s="9"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="27">
         <v>237</v>
       </c>
@@ -6511,7 +6600,7 @@
       <c r="F217" s="9"/>
       <c r="G217" s="9"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="27">
         <v>238</v>
       </c>
@@ -6526,7 +6615,7 @@
       <c r="F218" s="9"/>
       <c r="G218" s="9"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="27">
         <v>239</v>
       </c>
@@ -6541,7 +6630,7 @@
       <c r="F219" s="9"/>
       <c r="G219" s="9"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" s="27">
         <v>240</v>
       </c>
@@ -6556,7 +6645,7 @@
       <c r="F220" s="9"/>
       <c r="G220" s="9"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" s="27">
         <v>241</v>
       </c>
@@ -6571,7 +6660,7 @@
       <c r="F221" s="9"/>
       <c r="G221" s="9"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222" s="27">
         <v>242</v>
       </c>
@@ -6586,7 +6675,7 @@
       <c r="F222" s="9"/>
       <c r="G222" s="9"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223" s="27">
         <v>243</v>
       </c>
@@ -6601,7 +6690,7 @@
       <c r="F223" s="9"/>
       <c r="G223" s="9"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" s="27">
         <v>244</v>
       </c>
@@ -6616,7 +6705,7 @@
       <c r="F224" s="9"/>
       <c r="G224" s="9"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" s="27">
         <v>245</v>
       </c>
@@ -6631,7 +6720,7 @@
       <c r="F225" s="9"/>
       <c r="G225" s="9"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226" s="28">
         <v>246</v>
       </c>
@@ -6646,7 +6735,7 @@
       <c r="F226" s="9"/>
       <c r="G226" s="9"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" s="10">
         <v>247</v>
       </c>
@@ -6660,7 +6749,7 @@
       <c r="F227" s="9"/>
       <c r="G227" s="3"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" s="29">
         <v>248</v>
       </c>
@@ -6675,7 +6764,7 @@
       <c r="F228" s="9"/>
       <c r="G228" s="9"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" s="27">
         <v>249</v>
       </c>
@@ -6690,7 +6779,7 @@
       <c r="F229" s="9"/>
       <c r="G229" s="9"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" s="27">
         <v>250</v>
       </c>
@@ -6705,7 +6794,7 @@
       <c r="F230" s="9"/>
       <c r="G230" s="9"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" s="27">
         <v>251</v>
       </c>
@@ -6719,7 +6808,7 @@
       <c r="F231" s="9"/>
       <c r="G231" s="9"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" s="27">
         <v>252</v>
       </c>
@@ -6734,7 +6823,7 @@
       <c r="F232" s="9"/>
       <c r="G232" s="9"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" s="27">
         <v>253</v>
       </c>
@@ -6748,7 +6837,7 @@
       <c r="F233" s="9"/>
       <c r="G233" s="9"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" s="27">
         <v>254</v>
       </c>
@@ -6763,7 +6852,7 @@
       <c r="F234" s="9"/>
       <c r="G234" s="9"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" s="27">
         <v>255</v>
       </c>
@@ -6778,7 +6867,7 @@
       <c r="F235" s="9"/>
       <c r="G235" s="9"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" s="27">
         <v>256</v>
       </c>
@@ -6794,7 +6883,7 @@
       <c r="G236" s="9"/>
       <c r="J236" s="30"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" s="27">
         <v>257</v>
       </c>
@@ -6809,7 +6898,7 @@
       <c r="F237" s="9"/>
       <c r="G237" s="9"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238" s="27">
         <v>258</v>
       </c>
@@ -6824,7 +6913,7 @@
       <c r="F238" s="9"/>
       <c r="G238" s="9"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A239" s="27">
         <v>259</v>
       </c>
@@ -6839,7 +6928,7 @@
       <c r="F239" s="9"/>
       <c r="G239" s="9"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" s="27">
         <v>260</v>
       </c>
@@ -6854,7 +6943,7 @@
       <c r="F240" s="9"/>
       <c r="G240" s="9"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241" s="27">
         <v>261</v>
       </c>
@@ -6869,7 +6958,7 @@
       <c r="F241" s="9"/>
       <c r="G241" s="9"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242" s="27">
         <v>262</v>
       </c>
@@ -6884,7 +6973,7 @@
       <c r="F242" s="9"/>
       <c r="G242" s="15"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243" s="27">
         <v>263</v>
       </c>
@@ -6900,7 +6989,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244" s="27">
         <v>264</v>
       </c>
@@ -6915,7 +7004,7 @@
       <c r="F244" s="9"/>
       <c r="G244" s="9"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245" s="27">
         <v>265</v>
       </c>
@@ -6930,7 +7019,7 @@
       <c r="F245" s="9"/>
       <c r="G245" s="9"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246" s="27">
         <v>266</v>
       </c>
@@ -6945,7 +7034,7 @@
       <c r="F246" s="9"/>
       <c r="G246" s="9"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247" s="27">
         <v>267</v>
       </c>
@@ -6960,7 +7049,7 @@
       <c r="F247" s="9"/>
       <c r="G247" s="9"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248" s="27">
         <v>268</v>
       </c>
@@ -6975,7 +7064,7 @@
       <c r="F248" s="9"/>
       <c r="G248" s="9"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249" s="27">
         <v>269</v>
       </c>
@@ -6990,7 +7079,7 @@
       <c r="F249" s="9"/>
       <c r="G249" s="9"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250" s="27">
         <v>270</v>
       </c>
@@ -7005,7 +7094,7 @@
       <c r="F250" s="9"/>
       <c r="G250" s="9"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251" s="27">
         <v>271</v>
       </c>
@@ -7020,7 +7109,7 @@
       <c r="F251" s="9"/>
       <c r="G251" s="15"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252" s="27">
         <v>272</v>
       </c>
@@ -7035,7 +7124,7 @@
       <c r="F252" s="9"/>
       <c r="G252" s="9"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253" s="27">
         <v>273</v>
       </c>
@@ -7050,7 +7139,7 @@
       <c r="F253" s="9"/>
       <c r="G253" s="9"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254" s="27">
         <v>274</v>
       </c>
@@ -7065,7 +7154,7 @@
       <c r="F254" s="9"/>
       <c r="G254" s="9"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255" s="27">
         <v>275</v>
       </c>
@@ -7080,7 +7169,7 @@
       <c r="F255" s="9"/>
       <c r="G255" s="9"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256" s="27">
         <v>276</v>
       </c>
@@ -7095,7 +7184,7 @@
       <c r="F256" s="9"/>
       <c r="G256" s="15"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257" s="27">
         <v>277</v>
       </c>
@@ -7110,7 +7199,7 @@
       <c r="F257" s="9"/>
       <c r="G257" s="9"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258" s="27">
         <v>278</v>
       </c>
@@ -7125,7 +7214,7 @@
       <c r="F258" s="9"/>
       <c r="G258" s="9"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259" s="27">
         <v>279</v>
       </c>
@@ -7140,7 +7229,7 @@
       <c r="F259" s="9"/>
       <c r="G259" s="15"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260" s="27">
         <v>280</v>
       </c>
@@ -7155,7 +7244,7 @@
       <c r="F260" s="9"/>
       <c r="G260" s="9"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261" s="27">
         <v>281</v>
       </c>
@@ -7170,7 +7259,7 @@
       <c r="F261" s="9"/>
       <c r="G261" s="9"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" s="27">
         <v>282</v>
       </c>
@@ -7185,7 +7274,7 @@
       <c r="F262" s="9"/>
       <c r="G262" s="9"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263" s="27">
         <v>283</v>
       </c>
@@ -7200,7 +7289,7 @@
       <c r="F263" s="9"/>
       <c r="G263" s="9"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264" s="27">
         <v>284</v>
       </c>
@@ -7215,7 +7304,7 @@
       <c r="F264" s="9"/>
       <c r="G264" s="15"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265" s="27">
         <v>285</v>
       </c>
@@ -7230,7 +7319,7 @@
       <c r="F265" s="9"/>
       <c r="G265" s="9"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266" s="27">
         <v>286</v>
       </c>
@@ -7245,7 +7334,7 @@
       <c r="F266" s="9"/>
       <c r="G266" s="9"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267" s="27">
         <v>287</v>
       </c>
@@ -7260,7 +7349,7 @@
       <c r="F267" s="9"/>
       <c r="G267" s="15"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268" s="27">
         <v>288</v>
       </c>
@@ -7276,7 +7365,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269" s="27">
         <v>289</v>
       </c>
@@ -7289,7 +7378,7 @@
       <c r="F269" s="9"/>
       <c r="G269" s="9"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270" s="27">
         <v>290</v>
       </c>
@@ -7304,7 +7393,7 @@
       <c r="F270" s="9"/>
       <c r="G270" s="9"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271" s="27">
         <v>291</v>
       </c>
@@ -7319,7 +7408,7 @@
       <c r="F271" s="9"/>
       <c r="G271" s="9"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272" s="27">
         <v>292</v>
       </c>
@@ -7334,7 +7423,7 @@
       <c r="F272" s="9"/>
       <c r="G272" s="15"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273" s="27">
         <v>293</v>
       </c>
@@ -7349,7 +7438,7 @@
       <c r="F273" s="9"/>
       <c r="G273" s="9"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274" s="27">
         <v>294</v>
       </c>
@@ -7364,7 +7453,7 @@
       <c r="F274" s="9"/>
       <c r="G274" s="9"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275" s="27">
         <v>295</v>
       </c>
@@ -7379,7 +7468,7 @@
       <c r="F275" s="9"/>
       <c r="G275" s="15"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276" s="27">
         <v>296</v>
       </c>
@@ -7394,7 +7483,7 @@
       <c r="F276" s="9"/>
       <c r="G276" s="9"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277" s="27">
         <v>297</v>
       </c>
@@ -7409,7 +7498,7 @@
       <c r="F277" s="9"/>
       <c r="G277" s="9"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278" s="27">
         <v>298</v>
       </c>
@@ -7424,7 +7513,7 @@
       <c r="F278" s="9"/>
       <c r="G278" s="9"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A279" s="27">
         <v>299</v>
       </c>
@@ -7439,7 +7528,7 @@
       <c r="F279" s="9"/>
       <c r="G279" s="9"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280" s="27">
         <v>300</v>
       </c>
@@ -7454,7 +7543,7 @@
       <c r="F280" s="9"/>
       <c r="G280" s="15"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281" s="27">
         <v>301</v>
       </c>
@@ -7469,7 +7558,7 @@
       <c r="F281" s="9"/>
       <c r="G281" s="9"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282" s="27">
         <v>302</v>
       </c>
@@ -7484,7 +7573,7 @@
       <c r="F282" s="9"/>
       <c r="G282" s="9"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283" s="27">
         <v>303</v>
       </c>
@@ -7499,7 +7588,7 @@
       <c r="F283" s="9"/>
       <c r="G283" s="15"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284" s="27">
         <v>304</v>
       </c>
@@ -7514,7 +7603,7 @@
       <c r="F284" s="9"/>
       <c r="G284" s="9"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285" s="27">
         <v>305</v>
       </c>
@@ -7529,7 +7618,7 @@
       <c r="F285" s="9"/>
       <c r="G285" s="9"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286" s="27">
         <v>306</v>
       </c>
@@ -7544,7 +7633,7 @@
       <c r="F286" s="9"/>
       <c r="G286" s="9"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287" s="27">
         <v>307</v>
       </c>
@@ -7562,7 +7651,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288" s="27">
         <v>308</v>
       </c>
@@ -7575,7 +7664,7 @@
       <c r="F288" s="9"/>
       <c r="G288" s="15"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="27">
         <v>309</v>
       </c>
@@ -7590,7 +7679,7 @@
       <c r="F289" s="9"/>
       <c r="G289" s="9"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="27">
         <v>310</v>
       </c>
@@ -7605,7 +7694,7 @@
       <c r="F290" s="9"/>
       <c r="G290" s="9"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="27">
         <v>311</v>
       </c>
@@ -7620,7 +7709,7 @@
       <c r="F291" s="9"/>
       <c r="G291" s="15"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="27">
         <v>312</v>
       </c>
@@ -7635,7 +7724,7 @@
       <c r="F292" s="9"/>
       <c r="G292" s="9"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="27">
         <v>313</v>
       </c>
@@ -7650,7 +7739,7 @@
       <c r="F293" s="9"/>
       <c r="G293" s="9"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="27">
         <v>314</v>
       </c>
@@ -7665,7 +7754,7 @@
       <c r="F294" s="9"/>
       <c r="G294" s="9"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="27">
         <v>315</v>
       </c>
@@ -7680,7 +7769,7 @@
       <c r="F295" s="9"/>
       <c r="G295" s="9"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="27">
         <v>316</v>
       </c>
@@ -7695,7 +7784,7 @@
       <c r="F296" s="9"/>
       <c r="G296" s="15"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="27">
         <v>317</v>
       </c>
@@ -7710,7 +7799,7 @@
       <c r="F297" s="9"/>
       <c r="G297" s="9"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="27">
         <v>318</v>
       </c>
@@ -7725,7 +7814,7 @@
       <c r="F298" s="9"/>
       <c r="G298" s="9"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="27">
         <v>319</v>
       </c>
@@ -7740,7 +7829,7 @@
       <c r="F299" s="9"/>
       <c r="G299" s="15"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="27">
         <v>320</v>
       </c>
@@ -7755,7 +7844,7 @@
       <c r="F300" s="9"/>
       <c r="G300" s="9"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="27">
         <v>321</v>
       </c>
@@ -7770,7 +7859,7 @@
       <c r="F301" s="9"/>
       <c r="G301" s="9"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="27">
         <v>322</v>
       </c>
@@ -7785,7 +7874,7 @@
       <c r="F302" s="9"/>
       <c r="G302" s="9"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="27">
         <v>323</v>
       </c>
@@ -7800,7 +7889,7 @@
       <c r="F303" s="9"/>
       <c r="G303" s="9"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="27">
         <v>324</v>
       </c>
@@ -7815,7 +7904,7 @@
       <c r="F304" s="9"/>
       <c r="G304" s="15"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A305" s="27">
         <v>325</v>
       </c>
@@ -7830,7 +7919,7 @@
       <c r="F305" s="9"/>
       <c r="G305" s="9"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A306" s="27">
         <v>326</v>
       </c>
@@ -7845,7 +7934,7 @@
       <c r="F306" s="9"/>
       <c r="G306" s="9"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A307" s="27">
         <v>327</v>
       </c>
@@ -7860,7 +7949,7 @@
       <c r="F307" s="9"/>
       <c r="G307" s="15"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A308" s="27">
         <v>328</v>
       </c>
@@ -7875,7 +7964,7 @@
       <c r="F308" s="9"/>
       <c r="G308" s="9"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A309" s="27">
         <v>329</v>
       </c>
@@ -7890,7 +7979,7 @@
       <c r="F309" s="9"/>
       <c r="G309" s="9"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A310" s="27">
         <v>330</v>
       </c>
@@ -7905,7 +7994,7 @@
       <c r="F310" s="9"/>
       <c r="G310" s="9"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A311" s="27">
         <v>331</v>
       </c>
@@ -7920,7 +8009,7 @@
       <c r="F311" s="9"/>
       <c r="G311" s="9"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A312" s="27">
         <v>332</v>
       </c>
@@ -7938,7 +8027,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A313" s="27">
         <v>333</v>
       </c>
@@ -7951,7 +8040,7 @@
       <c r="F313" s="9"/>
       <c r="G313" s="9"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A314" s="27">
         <v>334</v>
       </c>
@@ -7966,7 +8055,7 @@
       <c r="F314" s="9"/>
       <c r="G314" s="9"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A315" s="27">
         <v>335</v>
       </c>
@@ -7981,7 +8070,7 @@
       <c r="F315" s="9"/>
       <c r="G315" s="15"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A316" s="27">
         <v>336</v>
       </c>
@@ -7996,7 +8085,7 @@
       <c r="F316" s="9"/>
       <c r="G316" s="9"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A317" s="27">
         <v>337</v>
       </c>
@@ -8011,7 +8100,7 @@
       <c r="F317" s="9"/>
       <c r="G317" s="9"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A318" s="27">
         <v>338</v>
       </c>
@@ -8026,7 +8115,7 @@
       <c r="F318" s="9"/>
       <c r="G318" s="9"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A319" s="27">
         <v>339</v>
       </c>
@@ -8041,7 +8130,7 @@
       <c r="F319" s="9"/>
       <c r="G319" s="9"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A320" s="27">
         <v>340</v>
       </c>
@@ -8056,7 +8145,7 @@
       <c r="F320" s="9"/>
       <c r="G320" s="9"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A321" s="27">
         <v>341</v>
       </c>
@@ -8071,7 +8160,7 @@
       <c r="F321" s="9"/>
       <c r="G321" s="9"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A322" s="27">
         <v>342</v>
       </c>
@@ -8086,7 +8175,7 @@
       <c r="F322" s="9"/>
       <c r="G322" s="9"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A323" s="27">
         <v>343</v>
       </c>
@@ -8101,7 +8190,7 @@
       <c r="F323" s="9"/>
       <c r="G323" s="9"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A324" s="27">
         <v>344</v>
       </c>
@@ -8116,7 +8205,7 @@
       <c r="F324" s="9"/>
       <c r="G324" s="9"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A325" s="27">
         <v>345</v>
       </c>
@@ -8131,7 +8220,7 @@
       <c r="F325" s="9"/>
       <c r="G325" s="9"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326" s="27">
         <v>346</v>
       </c>
@@ -8146,7 +8235,7 @@
       <c r="F326" s="9"/>
       <c r="G326" s="9"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A327" s="27">
         <v>347</v>
       </c>
@@ -8161,7 +8250,7 @@
       <c r="F327" s="9"/>
       <c r="G327" s="9"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A328" s="27">
         <v>348</v>
       </c>
@@ -8176,7 +8265,7 @@
       <c r="F328" s="9"/>
       <c r="G328" s="9"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329" s="27">
         <v>349</v>
       </c>
@@ -8191,7 +8280,7 @@
       <c r="F329" s="9"/>
       <c r="G329" s="9"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330" s="27">
         <v>350</v>
       </c>
@@ -8206,7 +8295,7 @@
       <c r="F330" s="9"/>
       <c r="G330" s="9"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331" s="27">
         <v>351</v>
       </c>
@@ -8221,7 +8310,7 @@
       <c r="F331" s="9"/>
       <c r="G331" s="9"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332" s="27">
         <v>352</v>
       </c>
@@ -8236,7 +8325,7 @@
       <c r="F332" s="9"/>
       <c r="G332" s="9"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A333" s="27">
         <v>353</v>
       </c>
@@ -8252,7 +8341,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334" s="27">
         <v>354</v>
       </c>
@@ -8267,7 +8356,7 @@
       <c r="F334" s="9"/>
       <c r="G334" s="9"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A335" s="27">
         <v>355</v>
       </c>
@@ -8282,7 +8371,7 @@
       <c r="F335" s="9"/>
       <c r="G335" s="9"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A336" s="27">
         <v>356</v>
       </c>
@@ -8297,7 +8386,7 @@
       <c r="F336" s="9"/>
       <c r="G336" s="9"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" s="27">
         <v>357</v>
       </c>
@@ -8312,7 +8401,7 @@
       <c r="F337" s="9"/>
       <c r="G337" s="9"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" s="27">
         <v>358</v>
       </c>
@@ -8327,7 +8416,7 @@
       <c r="F338" s="9"/>
       <c r="G338" s="9"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="27">
         <v>359</v>
       </c>
@@ -8342,7 +8431,7 @@
       <c r="F339" s="9"/>
       <c r="G339" s="9"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" s="27">
         <v>360</v>
       </c>
@@ -8357,7 +8446,7 @@
       <c r="F340" s="9"/>
       <c r="G340" s="9"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" s="27">
         <v>361</v>
       </c>
@@ -8372,7 +8461,7 @@
       <c r="F341" s="9"/>
       <c r="G341" s="9"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" s="27">
         <v>362</v>
       </c>
@@ -8387,7 +8476,7 @@
       <c r="F342" s="9"/>
       <c r="G342" s="9"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="27">
         <v>363</v>
       </c>
@@ -8402,7 +8491,7 @@
       <c r="F343" s="9"/>
       <c r="G343" s="9"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" s="27">
         <v>364</v>
       </c>
@@ -8417,7 +8506,7 @@
       <c r="F344" s="9"/>
       <c r="G344" s="9"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" s="27">
         <v>365</v>
       </c>
@@ -8432,7 +8521,7 @@
       <c r="F345" s="9"/>
       <c r="G345" s="9"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="27">
         <v>366</v>
       </c>
@@ -8447,7 +8536,7 @@
       <c r="F346" s="9"/>
       <c r="G346" s="9"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" s="27">
         <v>367</v>
       </c>
@@ -8462,7 +8551,7 @@
       <c r="F347" s="9"/>
       <c r="G347" s="9"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" s="27">
         <v>368</v>
       </c>
@@ -8477,7 +8566,7 @@
       <c r="F348" s="9"/>
       <c r="G348" s="9"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" s="27">
         <v>369</v>
       </c>
@@ -8492,7 +8581,7 @@
       <c r="F349" s="9"/>
       <c r="G349" s="9"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" s="27">
         <v>370</v>
       </c>
@@ -8507,7 +8596,7 @@
       <c r="F350" s="9"/>
       <c r="G350" s="9"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="27">
         <v>371</v>
       </c>
@@ -8522,7 +8611,7 @@
       <c r="F351" s="9"/>
       <c r="G351" s="9"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="27">
         <v>372</v>
       </c>
@@ -8537,7 +8626,7 @@
       <c r="F352" s="9"/>
       <c r="G352" s="9"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A353" s="27">
         <v>373</v>
       </c>
@@ -8552,7 +8641,7 @@
       <c r="F353" s="9"/>
       <c r="G353" s="9"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A354" s="27">
         <v>374</v>
       </c>
@@ -8567,7 +8656,7 @@
       <c r="F354" s="9"/>
       <c r="G354" s="9"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A355" s="27">
         <v>375</v>
       </c>
@@ -8582,7 +8671,7 @@
       <c r="F355" s="9"/>
       <c r="G355" s="9"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A356" s="27">
         <v>376</v>
       </c>
@@ -8597,7 +8686,7 @@
       <c r="F356" s="9"/>
       <c r="G356" s="9"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A357" s="27">
         <v>377</v>
       </c>
@@ -8615,7 +8704,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A358" s="27">
         <v>378</v>
       </c>
@@ -8628,7 +8717,7 @@
       <c r="F358" s="9"/>
       <c r="G358" s="9"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A359" s="27">
         <v>379</v>
       </c>
@@ -8643,7 +8732,7 @@
       <c r="F359" s="9"/>
       <c r="G359" s="9"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A360" s="27">
         <v>380</v>
       </c>
@@ -8658,7 +8747,7 @@
       <c r="F360" s="9"/>
       <c r="G360" s="9"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A361" s="27">
         <v>381</v>
       </c>
@@ -8673,7 +8762,7 @@
       <c r="F361" s="9"/>
       <c r="G361" s="9"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A362" s="27">
         <v>382</v>
       </c>
@@ -8688,7 +8777,7 @@
       <c r="F362" s="9"/>
       <c r="G362" s="9"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A363" s="27">
         <v>383</v>
       </c>
@@ -8703,7 +8792,7 @@
       <c r="F363" s="9"/>
       <c r="G363" s="9"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A364" s="27">
         <v>384</v>
       </c>
@@ -8718,7 +8807,7 @@
       <c r="F364" s="9"/>
       <c r="G364" s="9"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A365" s="27">
         <v>385</v>
       </c>
@@ -8733,7 +8822,7 @@
       <c r="F365" s="9"/>
       <c r="G365" s="9"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A366" s="27">
         <v>386</v>
       </c>
@@ -8748,7 +8837,7 @@
       <c r="F366" s="9"/>
       <c r="G366" s="9"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A367" s="27">
         <v>387</v>
       </c>
@@ -8763,7 +8852,7 @@
       <c r="F367" s="9"/>
       <c r="G367" s="9"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A368" s="27">
         <v>388</v>
       </c>
@@ -8778,7 +8867,7 @@
       <c r="F368" s="9"/>
       <c r="G368" s="9"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A369" s="27">
         <v>389</v>
       </c>
@@ -8793,7 +8882,7 @@
       <c r="F369" s="9"/>
       <c r="G369" s="9"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A370" s="27">
         <v>390</v>
       </c>
@@ -8808,7 +8897,7 @@
       <c r="F370" s="9"/>
       <c r="G370" s="9"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A371" s="27">
         <v>391</v>
       </c>
@@ -8823,7 +8912,7 @@
       <c r="F371" s="9"/>
       <c r="G371" s="9"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A372" s="27">
         <v>392</v>
       </c>
@@ -8840,7 +8929,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A373" s="27">
         <v>393</v>
       </c>
@@ -8855,7 +8944,7 @@
       <c r="F373" s="9"/>
       <c r="G373" s="9"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A374" s="27">
         <v>394</v>
       </c>
@@ -8870,7 +8959,7 @@
       <c r="F374" s="9"/>
       <c r="G374" s="9"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A375" s="27">
         <v>395</v>
       </c>
@@ -8885,7 +8974,7 @@
       <c r="F375" s="9"/>
       <c r="G375" s="9"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A376" s="27">
         <v>396</v>
       </c>
@@ -8900,7 +8989,7 @@
       <c r="F376" s="9"/>
       <c r="G376" s="9"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A377" s="27">
         <v>397</v>
       </c>
@@ -8915,7 +9004,7 @@
       <c r="F377" s="9"/>
       <c r="G377" s="9"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A378" s="27">
         <v>398</v>
       </c>
@@ -8931,7 +9020,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A379" s="27">
         <v>399</v>
       </c>
@@ -8945,7 +9034,7 @@
       </c>
       <c r="G379" s="9"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A380" s="27">
         <v>400</v>
       </c>
@@ -8960,7 +9049,7 @@
       <c r="F380" s="9"/>
       <c r="G380" s="9"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A381" s="27">
         <v>401</v>
       </c>
@@ -8975,7 +9064,7 @@
       <c r="F381" s="9"/>
       <c r="G381" s="9"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A382" s="27">
         <v>402</v>
       </c>
@@ -8990,7 +9079,7 @@
       <c r="F382" s="9"/>
       <c r="G382" s="9"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A383" s="27">
         <v>403</v>
       </c>
@@ -9005,7 +9094,7 @@
       <c r="F383" s="9"/>
       <c r="G383" s="9"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A384" s="27">
         <v>404</v>
       </c>
@@ -9020,7 +9109,7 @@
       <c r="F384" s="9"/>
       <c r="G384" s="9"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="27">
         <v>405</v>
       </c>
@@ -9035,7 +9124,7 @@
       <c r="F385" s="9"/>
       <c r="G385" s="9"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="27">
         <v>406</v>
       </c>
@@ -9050,7 +9139,7 @@
       <c r="F386" s="9"/>
       <c r="G386" s="9"/>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="27">
         <v>407</v>
       </c>
@@ -9065,7 +9154,7 @@
       <c r="F387" s="9"/>
       <c r="G387" s="9"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="27">
         <v>408</v>
       </c>
@@ -9080,7 +9169,7 @@
       <c r="F388" s="9"/>
       <c r="G388" s="9"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="27">
         <v>409</v>
       </c>
@@ -9095,7 +9184,7 @@
       <c r="F389" s="9"/>
       <c r="G389" s="9"/>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" s="27">
         <v>410</v>
       </c>
@@ -9110,7 +9199,7 @@
       <c r="F390" s="9"/>
       <c r="G390" s="9"/>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" s="27">
         <v>411</v>
       </c>
@@ -9121,7 +9210,7 @@
       <c r="F391" s="9"/>
       <c r="G391" s="9"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" s="27">
         <v>412</v>
       </c>
@@ -9132,7 +9221,7 @@
       <c r="F392" s="9"/>
       <c r="G392" s="9"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" s="27">
         <v>413</v>
       </c>
@@ -9143,7 +9232,7 @@
       <c r="F393" s="9"/>
       <c r="G393" s="9"/>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" s="27">
         <v>414</v>
       </c>
@@ -9154,7 +9243,7 @@
       <c r="F394" s="9"/>
       <c r="G394" s="9"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" s="27">
         <v>415</v>
       </c>
@@ -9165,7 +9254,7 @@
       <c r="F395" s="9"/>
       <c r="G395" s="9"/>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" s="27">
         <v>416</v>
       </c>
@@ -9176,7 +9265,7 @@
       <c r="F396" s="9"/>
       <c r="G396" s="9"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" s="27">
         <v>417</v>
       </c>
@@ -9187,7 +9276,7 @@
       <c r="F397" s="9"/>
       <c r="G397" s="9"/>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" s="27">
         <v>418</v>
       </c>
@@ -9198,7 +9287,7 @@
       <c r="F398" s="9"/>
       <c r="G398" s="9"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" s="27">
         <v>419</v>
       </c>
@@ -9209,7 +9298,7 @@
       <c r="F399" s="9"/>
       <c r="G399" s="9"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" s="27">
         <v>420</v>
       </c>
@@ -9220,7 +9309,7 @@
       <c r="F400" s="9"/>
       <c r="G400" s="9"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" s="27">
         <v>421</v>
       </c>
@@ -9231,7 +9320,7 @@
       <c r="F401" s="9"/>
       <c r="G401" s="9"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" s="27">
         <v>422</v>
       </c>
@@ -9242,7 +9331,7 @@
       <c r="F402" s="9"/>
       <c r="G402" s="9"/>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" s="27">
         <v>423</v>
       </c>
@@ -9253,7 +9342,7 @@
       <c r="F403" s="9"/>
       <c r="G403" s="9"/>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" s="27">
         <v>424</v>
       </c>
@@ -9264,7 +9353,7 @@
       <c r="F404" s="9"/>
       <c r="G404" s="9"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" s="27">
         <v>425</v>
       </c>
@@ -9275,7 +9364,7 @@
       <c r="F405" s="9"/>
       <c r="G405" s="9"/>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" s="27">
         <v>426</v>
       </c>
@@ -9286,7 +9375,7 @@
       <c r="F406" s="9"/>
       <c r="G406" s="9"/>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" s="27">
         <v>427</v>
       </c>
@@ -9297,7 +9386,7 @@
       <c r="F407" s="9"/>
       <c r="G407" s="9"/>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" s="27">
         <v>428</v>
       </c>
@@ -9308,7 +9397,7 @@
       <c r="F408" s="9"/>
       <c r="G408" s="9"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" s="27">
         <v>429</v>
       </c>
@@ -9319,7 +9408,7 @@
       <c r="F409" s="9"/>
       <c r="G409" s="9"/>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" s="27">
         <v>430</v>
       </c>
@@ -9330,7 +9419,7 @@
       <c r="F410" s="9"/>
       <c r="G410" s="9"/>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" s="27">
         <v>431</v>
       </c>
@@ -9341,7 +9430,7 @@
       <c r="F411" s="9"/>
       <c r="G411" s="9"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" s="27">
         <v>432</v>
       </c>
@@ -9352,7 +9441,7 @@
       <c r="F412" s="9"/>
       <c r="G412" s="9"/>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" s="27">
         <v>433</v>
       </c>
@@ -9363,7 +9452,7 @@
       <c r="F413" s="9"/>
       <c r="G413" s="9"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" s="27">
         <v>434</v>
       </c>
@@ -9374,7 +9463,7 @@
       <c r="F414" s="9"/>
       <c r="G414" s="9"/>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" s="27">
         <v>435</v>
       </c>
@@ -9385,7 +9474,7 @@
       <c r="F415" s="9"/>
       <c r="G415" s="9"/>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" s="27">
         <v>436</v>
       </c>
@@ -9396,7 +9485,7 @@
       <c r="F416" s="9"/>
       <c r="G416" s="9"/>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" s="27">
         <v>437</v>
       </c>
@@ -9407,7 +9496,7 @@
       <c r="F417" s="9"/>
       <c r="G417" s="9"/>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" s="27">
         <v>438</v>
       </c>
@@ -9418,7 +9507,7 @@
       <c r="F418" s="9"/>
       <c r="G418" s="9"/>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" s="27">
         <v>439</v>
       </c>
@@ -9429,7 +9518,7 @@
       <c r="F419" s="9"/>
       <c r="G419" s="9"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" s="27">
         <v>440</v>
       </c>
@@ -9440,7 +9529,7 @@
       <c r="F420" s="9"/>
       <c r="G420" s="9"/>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" s="27">
         <v>441</v>
       </c>
@@ -9451,7 +9540,7 @@
       <c r="F421" s="9"/>
       <c r="G421" s="9"/>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" s="27">
         <v>442</v>
       </c>
@@ -9462,7 +9551,7 @@
       <c r="F422" s="9"/>
       <c r="G422" s="9"/>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" s="27">
         <v>443</v>
       </c>
@@ -9473,7 +9562,7 @@
       <c r="F423" s="9"/>
       <c r="G423" s="9"/>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" s="27">
         <v>444</v>
       </c>
@@ -9484,7 +9573,7 @@
       <c r="F424" s="9"/>
       <c r="G424" s="9"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" s="27">
         <v>445</v>
       </c>
@@ -9495,7 +9584,7 @@
       <c r="F425" s="9"/>
       <c r="G425" s="9"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" s="27">
         <v>446</v>
       </c>
@@ -9506,7 +9595,7 @@
       <c r="F426" s="9"/>
       <c r="G426" s="9"/>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" s="27">
         <v>447</v>
       </c>
@@ -9517,7 +9606,7 @@
       <c r="F427" s="9"/>
       <c r="G427" s="9"/>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" s="27">
         <v>448</v>
       </c>
@@ -9528,7 +9617,7 @@
       <c r="F428" s="9"/>
       <c r="G428" s="9"/>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" s="27">
         <v>449</v>
       </c>
@@ -9539,7 +9628,7 @@
       <c r="F429" s="9"/>
       <c r="G429" s="9"/>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" s="27">
         <v>450</v>
       </c>
@@ -9550,7 +9639,7 @@
       <c r="F430" s="9"/>
       <c r="G430" s="9"/>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" s="27">
         <v>451</v>
       </c>
@@ -9561,7 +9650,7 @@
       <c r="F431" s="9"/>
       <c r="G431" s="9"/>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" s="27">
         <v>452</v>
       </c>
@@ -9572,7 +9661,7 @@
       <c r="F432" s="9"/>
       <c r="G432" s="9"/>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" s="27">
         <v>453</v>
       </c>
@@ -9583,7 +9672,7 @@
       <c r="F433" s="9"/>
       <c r="G433" s="9"/>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="27">
         <v>454</v>
       </c>
@@ -9594,7 +9683,7 @@
       <c r="F434" s="9"/>
       <c r="G434" s="9"/>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="27">
         <v>455</v>
       </c>
@@ -9605,7 +9694,7 @@
       <c r="F435" s="9"/>
       <c r="G435" s="9"/>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="27">
         <v>456</v>
       </c>
@@ -9616,7 +9705,7 @@
       <c r="F436" s="9"/>
       <c r="G436" s="9"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="27">
         <v>457</v>
       </c>
@@ -9627,7 +9716,7 @@
       <c r="F437" s="9"/>
       <c r="G437" s="9"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="27">
         <v>458</v>
       </c>
@@ -9638,7 +9727,7 @@
       <c r="F438" s="9"/>
       <c r="G438" s="9"/>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="27">
         <v>459</v>
       </c>
@@ -9649,7 +9738,7 @@
       <c r="F439" s="9"/>
       <c r="G439" s="9"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" s="27">
         <v>460</v>
       </c>
@@ -9660,7 +9749,7 @@
       <c r="F440" s="9"/>
       <c r="G440" s="9"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" s="27">
         <v>461</v>
       </c>
@@ -9671,7 +9760,7 @@
       <c r="F441" s="9"/>
       <c r="G441" s="9"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" s="27">
         <v>462</v>
       </c>
@@ -9682,7 +9771,7 @@
       <c r="F442" s="9"/>
       <c r="G442" s="9"/>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" s="27">
         <v>463</v>
       </c>
@@ -9693,7 +9782,7 @@
       <c r="F443" s="9"/>
       <c r="G443" s="9"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" s="27">
         <v>464</v>
       </c>
@@ -9704,7 +9793,7 @@
       <c r="F444" s="9"/>
       <c r="G444" s="9"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" s="27">
         <v>465</v>
       </c>
@@ -9715,7 +9804,7 @@
       <c r="F445" s="9"/>
       <c r="G445" s="9"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446" s="27">
         <v>466</v>
       </c>
@@ -9726,7 +9815,7 @@
       <c r="F446" s="9"/>
       <c r="G446" s="9"/>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447" s="27">
         <v>467</v>
       </c>
@@ -9737,7 +9826,7 @@
       <c r="F447" s="9"/>
       <c r="G447" s="9"/>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448" s="27">
         <v>468</v>
       </c>
@@ -9748,7 +9837,7 @@
       <c r="F448" s="9"/>
       <c r="G448" s="9"/>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449" s="27">
         <v>469</v>
       </c>
@@ -9759,7 +9848,7 @@
       <c r="F449" s="9"/>
       <c r="G449" s="9"/>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A450" s="27">
         <v>470</v>
       </c>
@@ -9770,7 +9859,7 @@
       <c r="F450" s="9"/>
       <c r="G450" s="9"/>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A451" s="27">
         <v>471</v>
       </c>
@@ -9781,7 +9870,7 @@
       <c r="F451" s="9"/>
       <c r="G451" s="9"/>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A452" s="27">
         <v>472</v>
       </c>
@@ -9792,7 +9881,7 @@
       <c r="F452" s="9"/>
       <c r="G452" s="9"/>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A453" s="27">
         <v>473</v>
       </c>
@@ -9803,7 +9892,7 @@
       <c r="F453" s="9"/>
       <c r="G453" s="9"/>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A454" s="27">
         <v>474</v>
       </c>
@@ -9814,7 +9903,7 @@
       <c r="F454" s="9"/>
       <c r="G454" s="9"/>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A455" s="27">
         <v>475</v>
       </c>
@@ -9825,7 +9914,7 @@
       <c r="F455" s="9"/>
       <c r="G455" s="9"/>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A456" s="27">
         <v>476</v>
       </c>
@@ -9836,7 +9925,7 @@
       <c r="F456" s="9"/>
       <c r="G456" s="9"/>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A457" s="27">
         <v>477</v>
       </c>
@@ -9847,7 +9936,7 @@
       <c r="F457" s="9"/>
       <c r="G457" s="9"/>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A458" s="27">
         <v>478</v>
       </c>
@@ -9858,7 +9947,7 @@
       <c r="F458" s="9"/>
       <c r="G458" s="9"/>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A459" s="27">
         <v>479</v>
       </c>
@@ -9869,7 +9958,7 @@
       <c r="F459" s="9"/>
       <c r="G459" s="9"/>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A460" s="27">
         <v>480</v>
       </c>
@@ -9880,7 +9969,7 @@
       <c r="F460" s="9"/>
       <c r="G460" s="9"/>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A461" s="27">
         <v>481</v>
       </c>
@@ -9891,7 +9980,7 @@
       <c r="F461" s="9"/>
       <c r="G461" s="9"/>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A462" s="27">
         <v>482</v>
       </c>
@@ -9902,7 +9991,7 @@
       <c r="F462" s="9"/>
       <c r="G462" s="9"/>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A463" s="27">
         <v>483</v>
       </c>
@@ -9913,7 +10002,7 @@
       <c r="F463" s="9"/>
       <c r="G463" s="9"/>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A464" s="27">
         <v>484</v>
       </c>
@@ -9924,7 +10013,7 @@
       <c r="F464" s="9"/>
       <c r="G464" s="9"/>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A465" s="27">
         <v>485</v>
       </c>
@@ -9935,7 +10024,7 @@
       <c r="F465" s="9"/>
       <c r="G465" s="9"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A466" s="27">
         <v>486</v>
       </c>
@@ -9946,7 +10035,7 @@
       <c r="F466" s="9"/>
       <c r="G466" s="9"/>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A467" s="27">
         <v>487</v>
       </c>
@@ -9957,7 +10046,7 @@
       <c r="F467" s="9"/>
       <c r="G467" s="9"/>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A468" s="27">
         <v>488</v>
       </c>
@@ -9968,7 +10057,7 @@
       <c r="F468" s="9"/>
       <c r="G468" s="9"/>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A469" s="27">
         <v>489</v>
       </c>
@@ -9979,7 +10068,7 @@
       <c r="F469" s="9"/>
       <c r="G469" s="9"/>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A470" s="27">
         <v>490</v>
       </c>
@@ -9990,7 +10079,7 @@
       <c r="F470" s="9"/>
       <c r="G470" s="9"/>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A471" s="27">
         <v>491</v>
       </c>
@@ -10001,7 +10090,7 @@
       <c r="F471" s="9"/>
       <c r="G471" s="9"/>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A472" s="27">
         <v>492</v>
       </c>
@@ -10012,7 +10101,7 @@
       <c r="F472" s="9"/>
       <c r="G472" s="9"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A473" s="27">
         <v>493</v>
       </c>
@@ -10023,7 +10112,7 @@
       <c r="F473" s="9"/>
       <c r="G473" s="9"/>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A474" s="27">
         <v>494</v>
       </c>
@@ -10034,7 +10123,7 @@
       <c r="F474" s="9"/>
       <c r="G474" s="9"/>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A475" s="27">
         <v>495</v>
       </c>
@@ -10045,7 +10134,7 @@
       <c r="F475" s="9"/>
       <c r="G475" s="9"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A476" s="27">
         <v>496</v>
       </c>
@@ -10056,7 +10145,7 @@
       <c r="F476" s="9"/>
       <c r="G476" s="9"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A477" s="27">
         <v>497</v>
       </c>
@@ -10067,7 +10156,7 @@
       <c r="F477" s="9"/>
       <c r="G477" s="9"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A478" s="27">
         <v>498</v>
       </c>
@@ -10078,7 +10167,7 @@
       <c r="F478" s="9"/>
       <c r="G478" s="9"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A479" s="27">
         <v>499</v>
       </c>
@@ -10089,7 +10178,7 @@
       <c r="F479" s="9"/>
       <c r="G479" s="9"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D480" s="9"/>
       <c r="E480" s="9"/>
       <c r="F480" s="9"/>
@@ -10114,99 +10203,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
-    <col min="8" max="8" width="46.85546875" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.453125" customWidth="1"/>
+    <col min="8" max="8" width="46.81640625" customWidth="1"/>
+    <col min="9" max="9" width="31.453125" customWidth="1"/>
+    <col min="10" max="10" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="194" t="s">
+    <row r="1" spans="1:10" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="193" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
       <c r="I1" s="71"/>
     </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="196" t="s">
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
+      <c r="B2" s="196"/>
+      <c r="C2" s="196"/>
+      <c r="D2" s="196"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="196"/>
+      <c r="H2" s="196"/>
       <c r="I2" s="72"/>
     </row>
-    <row r="3" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="196" t="s">
+    <row r="3" spans="1:10" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
       <c r="I3" s="72"/>
     </row>
-    <row r="4" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="196" t="s">
+    <row r="4" spans="1:10" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="195" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="197"/>
+      <c r="B4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+      <c r="G4" s="196"/>
+      <c r="H4" s="196"/>
       <c r="I4" s="72"/>
     </row>
-    <row r="5" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="196" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="197"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="197"/>
-      <c r="G5" s="197"/>
-      <c r="H5" s="197"/>
+    <row r="5" spans="1:10" s="8" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="195" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="196"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="196"/>
       <c r="I5" s="72"/>
     </row>
-    <row r="6" spans="1:10" s="8" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="192" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="193"/>
-      <c r="C6" s="193"/>
-      <c r="D6" s="193"/>
-      <c r="E6" s="193"/>
-      <c r="F6" s="193"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="193"/>
+    <row r="6" spans="1:10" s="8" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="191" t="s">
+        <v>259</v>
+      </c>
+      <c r="B6" s="192"/>
+      <c r="C6" s="192"/>
+      <c r="D6" s="192"/>
+      <c r="E6" s="192"/>
+      <c r="F6" s="192"/>
+      <c r="G6" s="192"/>
+      <c r="H6" s="192"/>
       <c r="I6" s="72"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="73" t="s">
         <v>3</v>
       </c>
@@ -10214,7 +10303,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D7" s="74" t="s">
         <v>26</v>
@@ -10235,419 +10324,373 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="131"/>
-      <c r="B8" s="165"/>
+      <c r="B8" s="156"/>
       <c r="C8" s="133"/>
-      <c r="D8" s="180" t="s">
+      <c r="D8" s="183" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="135"/>
       <c r="F8" s="134"/>
       <c r="G8" s="136"/>
-      <c r="H8" s="132" t="s">
-        <v>260</v>
-      </c>
+      <c r="H8" s="132"/>
       <c r="I8" s="137"/>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="138"/>
       <c r="B9" s="123"/>
       <c r="C9" s="122"/>
-      <c r="D9" s="181"/>
+      <c r="D9" s="184"/>
       <c r="E9" s="14"/>
       <c r="F9" s="2"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="123" t="s">
-        <v>260</v>
-      </c>
+      <c r="H9" s="123"/>
       <c r="I9" s="139"/>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="138"/>
       <c r="B10" s="9"/>
       <c r="C10" s="122"/>
-      <c r="D10" s="181"/>
+      <c r="D10" s="184"/>
       <c r="E10" s="14"/>
       <c r="F10" s="2"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="123" t="s">
-        <v>261</v>
-      </c>
+      <c r="H10" s="123"/>
       <c r="I10" s="139"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="138"/>
       <c r="B11" s="9"/>
       <c r="C11" s="128"/>
-      <c r="D11" s="181"/>
+      <c r="D11" s="184"/>
       <c r="E11" s="14"/>
       <c r="F11" s="2"/>
       <c r="G11" s="10"/>
       <c r="H11" s="6"/>
       <c r="I11" s="139"/>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="138"/>
       <c r="B12" s="9"/>
       <c r="C12" s="122"/>
-      <c r="D12" s="181"/>
+      <c r="D12" s="184"/>
       <c r="E12" s="14"/>
       <c r="F12" s="2"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="123" t="s">
-        <v>165</v>
-      </c>
+      <c r="H12" s="123"/>
       <c r="I12" s="139"/>
       <c r="J12" s="125"/>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="138"/>
       <c r="B13" s="123"/>
       <c r="C13" s="122"/>
-      <c r="D13" s="181"/>
+      <c r="D13" s="184"/>
       <c r="E13" s="14"/>
       <c r="F13" s="2"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="123" t="s">
-        <v>260</v>
-      </c>
+      <c r="H13" s="123"/>
       <c r="I13" s="139"/>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="140"/>
-      <c r="B14" s="166"/>
+      <c r="B14" s="157"/>
       <c r="C14" s="141"/>
-      <c r="D14" s="182"/>
+      <c r="D14" s="185"/>
       <c r="E14" s="143"/>
       <c r="F14" s="142"/>
       <c r="G14" s="144"/>
-      <c r="H14" s="145" t="s">
-        <v>260</v>
-      </c>
+      <c r="H14" s="145"/>
       <c r="I14" s="146"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="185" t="s">
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="186" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="186"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="186"/>
-      <c r="G15" s="186"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="187"/>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="187"/>
+      <c r="C15" s="187"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="187"/>
+      <c r="G15" s="187"/>
+      <c r="H15" s="187"/>
+      <c r="I15" s="188"/>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="131"/>
-      <c r="B16" s="167"/>
-      <c r="C16" s="168"/>
-      <c r="D16" s="188" t="s">
-        <v>259</v>
+      <c r="B16" s="158"/>
+      <c r="C16" s="159"/>
+      <c r="D16" s="189" t="s">
+        <v>257</v>
       </c>
       <c r="E16" s="135"/>
       <c r="F16" s="134"/>
       <c r="G16" s="136"/>
-      <c r="H16" s="132" t="s">
-        <v>256</v>
-      </c>
+      <c r="H16" s="132"/>
       <c r="I16" s="137"/>
     </row>
-    <row r="17" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="138"/>
       <c r="B17" s="123"/>
       <c r="C17" s="122"/>
-      <c r="D17" s="189"/>
+      <c r="D17" s="190"/>
       <c r="E17" s="14"/>
       <c r="F17" s="2"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="9" t="s">
-        <v>262</v>
-      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="139"/>
     </row>
-    <row r="18" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="138"/>
       <c r="B18" s="87"/>
       <c r="C18" s="122"/>
-      <c r="D18" s="189"/>
+      <c r="D18" s="190"/>
       <c r="E18" s="14"/>
       <c r="F18" s="2"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="9" t="s">
-        <v>262</v>
-      </c>
+      <c r="H18" s="9"/>
       <c r="I18" s="139"/>
     </row>
-    <row r="19" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="138"/>
       <c r="B19" s="9"/>
       <c r="C19" s="128"/>
-      <c r="D19" s="189"/>
+      <c r="D19" s="190"/>
       <c r="F19" s="2"/>
       <c r="G19" s="10"/>
       <c r="H19" s="3"/>
       <c r="I19" s="139"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="138"/>
       <c r="B20" s="92"/>
       <c r="C20" s="122"/>
-      <c r="D20" s="189"/>
+      <c r="D20" s="190"/>
       <c r="E20" s="14"/>
       <c r="F20" s="2"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="9" t="s">
-        <v>262</v>
-      </c>
+      <c r="H20" s="9"/>
       <c r="I20" s="139"/>
     </row>
-    <row r="21" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="138"/>
       <c r="B21" s="123"/>
       <c r="C21" s="126"/>
-      <c r="D21" s="189"/>
+      <c r="D21" s="190"/>
       <c r="E21" s="14"/>
       <c r="F21" s="2"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="9" t="s">
-        <v>267</v>
-      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="139"/>
     </row>
-    <row r="22" spans="1:11" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="140"/>
-      <c r="B22" s="169"/>
-      <c r="C22" s="147"/>
+    <row r="22" spans="1:11" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="160"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="162"/>
       <c r="D22" s="190"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="I22" s="146"/>
-    </row>
-    <row r="23" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="131"/>
-      <c r="B23" s="153"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="191" t="s">
+      <c r="E22" s="197"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="204"/>
+    </row>
+    <row r="23" spans="1:11" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="205"/>
+      <c r="B23" s="206"/>
+      <c r="C23" s="206"/>
+      <c r="D23" s="206"/>
+      <c r="E23" s="206"/>
+      <c r="F23" s="206"/>
+      <c r="G23" s="206"/>
+      <c r="H23" s="206"/>
+      <c r="I23" s="207"/>
+    </row>
+    <row r="24" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="153"/>
+      <c r="B24" s="163"/>
+      <c r="C24" s="164"/>
+      <c r="D24" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="154"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="137"/>
-    </row>
-    <row r="24" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="156"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="183"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="I24" s="157"/>
-    </row>
-    <row r="25" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="156"/>
+      <c r="E24" s="165"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="166"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="154"/>
+    </row>
+    <row r="25" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="148"/>
       <c r="B25" s="124"/>
       <c r="C25" s="127"/>
-      <c r="D25" s="183"/>
+      <c r="D25" s="181"/>
       <c r="E25" s="14"/>
       <c r="F25" s="102"/>
       <c r="G25" s="86"/>
-      <c r="H25" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="I25" s="157"/>
-    </row>
-    <row r="26" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="156"/>
-      <c r="B26" s="165"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="149"/>
+    </row>
+    <row r="26" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="148"/>
+      <c r="B26" s="156"/>
       <c r="C26" s="126"/>
-      <c r="D26" s="183"/>
+      <c r="D26" s="181"/>
       <c r="E26" s="14"/>
       <c r="F26" s="102"/>
       <c r="G26" s="90"/>
-      <c r="H26" s="77" t="s">
-        <v>237</v>
-      </c>
-      <c r="I26" s="157"/>
-    </row>
-    <row r="27" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="156"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="149"/>
+    </row>
+    <row r="27" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="148"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="183"/>
+      <c r="D27" s="181"/>
       <c r="E27" s="83"/>
       <c r="F27" s="102"/>
       <c r="G27" s="102"/>
       <c r="H27" s="120"/>
-      <c r="I27" s="157"/>
-    </row>
-    <row r="28" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="156"/>
+      <c r="I27" s="149"/>
+    </row>
+    <row r="28" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="148"/>
       <c r="B28" s="87"/>
       <c r="C28" s="122"/>
-      <c r="D28" s="183"/>
+      <c r="D28" s="181"/>
       <c r="E28" s="14"/>
       <c r="F28" s="102"/>
       <c r="G28" s="90"/>
-      <c r="H28" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="I28" s="157"/>
-    </row>
-    <row r="29" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="156"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="149"/>
+    </row>
+    <row r="29" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="148"/>
       <c r="B29" s="124"/>
       <c r="C29" s="122"/>
-      <c r="D29" s="183"/>
+      <c r="D29" s="181"/>
       <c r="E29" s="14"/>
       <c r="F29" s="102"/>
       <c r="G29" s="86"/>
-      <c r="H29" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="I29" s="157"/>
-    </row>
-    <row r="30" spans="1:11" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="158"/>
-      <c r="B30" s="170"/>
-      <c r="C30" s="141"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="148" t="s">
-        <v>262</v>
-      </c>
-      <c r="I30" s="161"/>
-    </row>
-    <row r="31" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="162"/>
-      <c r="B31" s="150"/>
-      <c r="C31" s="151"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="149"/>
-      <c r="I31" s="163"/>
-    </row>
-    <row r="32" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="156"/>
-      <c r="B32" s="167"/>
-      <c r="C32" s="122"/>
-      <c r="D32" s="183" t="s">
+      <c r="H29" s="9"/>
+      <c r="I29" s="149"/>
+    </row>
+    <row r="30" spans="1:11" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="168"/>
+      <c r="B30" s="169"/>
+      <c r="C30" s="170"/>
+      <c r="D30" s="181"/>
+      <c r="E30" s="197"/>
+      <c r="F30" s="198"/>
+      <c r="G30" s="199"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="200"/>
+    </row>
+    <row r="31" spans="1:11" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="201"/>
+      <c r="B31" s="202"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="202"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="203"/>
+    </row>
+    <row r="32" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="153"/>
+      <c r="B32" s="171"/>
+      <c r="C32" s="164"/>
+      <c r="D32" s="181" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="14"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="I32" s="157"/>
-    </row>
-    <row r="33" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="156"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
+      <c r="H32" s="167"/>
+      <c r="I32" s="154"/>
+    </row>
+    <row r="33" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="148"/>
       <c r="B33" s="129"/>
       <c r="C33" s="126"/>
-      <c r="D33" s="183"/>
+      <c r="D33" s="181"/>
       <c r="E33" s="14"/>
       <c r="F33" s="102"/>
       <c r="G33" s="102"/>
-      <c r="H33" s="77" t="s">
-        <v>257</v>
-      </c>
-      <c r="I33" s="157"/>
-    </row>
-    <row r="34" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="156"/>
-      <c r="B34" s="167"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="149"/>
+    </row>
+    <row r="34" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="148"/>
+      <c r="B34" s="158"/>
       <c r="C34" s="122"/>
-      <c r="D34" s="183"/>
+      <c r="D34" s="181"/>
       <c r="E34" s="14"/>
       <c r="F34" s="102"/>
       <c r="G34" s="102"/>
-      <c r="H34" s="77" t="s">
-        <v>257</v>
-      </c>
-      <c r="I34" s="157"/>
-    </row>
-    <row r="35" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="156"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="149"/>
+    </row>
+    <row r="35" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="148"/>
       <c r="B35" s="130"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="183"/>
+      <c r="D35" s="181"/>
       <c r="E35" s="121"/>
       <c r="F35" s="102"/>
       <c r="G35" s="102"/>
       <c r="H35" s="77"/>
-      <c r="I35" s="157"/>
-    </row>
-    <row r="36" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="156"/>
+      <c r="I35" s="149"/>
+    </row>
+    <row r="36" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="148"/>
       <c r="B36" s="87"/>
       <c r="C36" s="122"/>
-      <c r="D36" s="183"/>
+      <c r="D36" s="181"/>
       <c r="E36" s="14"/>
       <c r="F36" s="102"/>
       <c r="G36" s="102"/>
-      <c r="H36" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="I36" s="157"/>
-    </row>
-    <row r="37" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="156"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="149"/>
+    </row>
+    <row r="37" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="148"/>
       <c r="B37" s="129"/>
       <c r="C37" s="122"/>
-      <c r="D37" s="183"/>
+      <c r="D37" s="181"/>
       <c r="E37" s="14"/>
       <c r="F37" s="102"/>
       <c r="G37" s="102"/>
-      <c r="H37" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="I37" s="157"/>
-    </row>
-    <row r="38" spans="1:9" s="103" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="158"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="149"/>
+    </row>
+    <row r="38" spans="1:9" s="103" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="150"/>
       <c r="B38" s="87"/>
       <c r="C38" s="141"/>
-      <c r="D38" s="184"/>
+      <c r="D38" s="182"/>
       <c r="E38" s="14"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="159"/>
-      <c r="H38" s="164" t="s">
-        <v>149</v>
-      </c>
-      <c r="I38" s="161"/>
+      <c r="F38" s="151"/>
+      <c r="G38" s="151"/>
+      <c r="H38" s="155"/>
+      <c r="I38" s="152"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="D32:D38"/>
+    <mergeCell ref="D24:D30"/>
     <mergeCell ref="D8:D14"/>
-    <mergeCell ref="D32:D38"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="D16:D22"/>
-    <mergeCell ref="D23:D30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A23:I23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="69" orientation="landscape" r:id="rId1"/>
@@ -10663,22 +10706,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22.7265625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>15</v>
       </c>
@@ -10698,7 +10741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>1</v>
       </c>
@@ -10708,7 +10751,7 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>2</v>
       </c>
@@ -10718,7 +10761,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>3</v>
       </c>
@@ -10728,7 +10771,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>4</v>
       </c>
@@ -10738,7 +10781,7 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>5</v>
       </c>
@@ -10748,7 +10791,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>6</v>
       </c>
@@ -10758,7 +10801,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>7</v>
       </c>
@@ -10768,7 +10811,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>8</v>
       </c>
@@ -10778,7 +10821,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>9</v>
       </c>
@@ -10788,7 +10831,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>10</v>
       </c>
@@ -10798,7 +10841,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>11</v>
       </c>
@@ -10808,7 +10851,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>12</v>
       </c>
@@ -10818,7 +10861,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>13</v>
       </c>
@@ -10828,7 +10871,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>14</v>
       </c>
@@ -10846,19 +10889,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -10869,98 +10912,98 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>1</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>3</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>4</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>5</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>6</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>7</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>8</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>9</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>10</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>11</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>12</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>13</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>14</v>
       </c>
